--- a/hira_material_automation/output/monthly/202601_202609__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04T23:24:20</t>
+          <t>2026-09-15T00:15:43</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3358ef2f6b9ed02775251923435bbfe7fe60094ef4808420846bed4923c5abd3</t>
+          <t>a2cc7abc80d1fdf1755d76f3d17b9be86a375e19f4346b4ecd1620cff6defc25</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202609__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-15T00:15:43</t>
+          <t>2026-09-25T00:19:13</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a2cc7abc80d1fdf1755d76f3d17b9be86a375e19f4346b4ecd1620cff6defc25</t>
+          <t>7266a7e416b5a26f11c4caadf46c4ec0ddb456445fff4b26a9f01e0c3ae9d4d3</t>
         </is>
       </c>
     </row>
